--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/27,07,26 Останкино КИ и ЗПФ/дв 27,07,26 млрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/27,07,26 Останкино КИ и ЗПФ/дв 27,07,26 млрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\27,07,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0F1154-0F20-4D6A-8158-25321DB031F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A7A511-856D-45E7-AEE6-BB2257BC8F07}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="176">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -660,7 +660,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -701,6 +701,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -737,7 +743,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -760,6 +766,10 @@
     <xf numFmtId="2" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -15063,94 +15073,96 @@
       <c r="AY86" s="8"/>
     </row>
     <row r="87" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C87" s="8">
+      <c r="C87" s="22">
         <v>87</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="22">
         <v>74</v>
       </c>
-      <c r="E87" s="8">
+      <c r="E87" s="22">
         <v>88</v>
       </c>
-      <c r="F87" s="8">
+      <c r="F87" s="22">
         <v>63</v>
       </c>
-      <c r="G87" s="6">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H87" s="8">
+      <c r="G87" s="23">
+        <v>0</v>
+      </c>
+      <c r="H87" s="22">
         <v>45</v>
       </c>
-      <c r="I87" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8">
+      <c r="I87" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="J87" s="22"/>
+      <c r="K87" s="22">
         <v>97</v>
       </c>
-      <c r="L87" s="8">
+      <c r="L87" s="22">
         <f t="shared" si="20"/>
         <v>-9</v>
       </c>
-      <c r="M87" s="8"/>
-      <c r="N87" s="8"/>
-      <c r="O87" s="8">
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22">
         <v>210</v>
       </c>
-      <c r="P87" s="8"/>
-      <c r="Q87" s="8">
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22">
         <f t="shared" si="21"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4">
+      <c r="R87" s="24"/>
+      <c r="S87" s="24">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="T87" s="15"/>
-      <c r="U87" s="8">
+      <c r="T87" s="25"/>
+      <c r="U87" s="22">
         <f t="shared" si="24"/>
         <v>15.511363636363635</v>
       </c>
-      <c r="V87" s="8">
+      <c r="V87" s="22">
         <f t="shared" si="22"/>
         <v>15.511363636363635</v>
       </c>
-      <c r="W87" s="8">
+      <c r="W87" s="22">
         <v>23.8</v>
       </c>
-      <c r="X87" s="8">
+      <c r="X87" s="22">
         <v>17.600000000000001</v>
       </c>
-      <c r="Y87" s="8">
+      <c r="Y87" s="22">
         <v>12.2</v>
       </c>
-      <c r="Z87" s="8">
+      <c r="Z87" s="22">
         <v>26.4</v>
       </c>
-      <c r="AA87" s="8">
+      <c r="AA87" s="22">
         <v>20</v>
       </c>
-      <c r="AB87" s="8">
+      <c r="AB87" s="22">
         <v>16.399999999999999</v>
       </c>
-      <c r="AC87" s="8">
+      <c r="AC87" s="22">
         <v>18.600000000000001</v>
       </c>
-      <c r="AD87" s="8">
+      <c r="AD87" s="22">
         <v>15.8</v>
       </c>
-      <c r="AE87" s="8">
+      <c r="AE87" s="22">
         <v>14.4</v>
       </c>
-      <c r="AF87" s="8"/>
-      <c r="AG87" s="8">
+      <c r="AF87" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG87" s="22">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
